--- a/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1394,17 +1386,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1484,17 +1468,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">

--- a/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1808015</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>180815</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1808015</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>180815</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1808015</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>180815</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>180815</t>
+          <t>1808015</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>180815</t>
+          <t>1808015</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>180815</t>
+          <t>1808015</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">

--- a/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
@@ -1610,31 +1610,83 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1808016</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>1808016</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="J10" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+      <c r="O10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n"/>
-      <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
+      <c r="X10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA10" s="6" t="n"/>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
@@ -1660,31 +1712,83 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1808016</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1808016</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
+      <c r="O11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -1710,31 +1814,83 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1808016</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>1808016</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>

--- a/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
+++ b/output/upload/S00026_1808_노후실손의료비보장보험_갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>50</v>
       </c>
@@ -1408,22 +1412,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1808015</t>
+          <t>1808016</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1808015</t>
+          <t>1808016</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
+          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1441,12 +1445,16 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -1508,83 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1808015</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1808015</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 상해형 무배당</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>109</v>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
-      <c r="X9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
+      <c r="Z9" s="6" t="n"/>
       <c r="AA9" s="6" t="n"/>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
@@ -1610,83 +1566,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="6" t="n"/>
+      <c r="Z10" s="6" t="n"/>
       <c r="AA10" s="6" t="n"/>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
@@ -1712,83 +1616,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -1814,83 +1666,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>1808016</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 노후실손의료비보장보험(갱신형) 질병형 무배당</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>109</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
